--- a/sheets/대금율보/검수/밀양아리랑 (b1_110_1).xlsx
+++ b/sheets/대금율보/검수/밀양아리랑 (b1_110_1).xlsx
@@ -2809,8 +2809,7 @@
         <is>
           <t xml:space="preserve">㴌
 –
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -2820,8 +2819,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -2833,8 +2831,7 @@
         <is>
           <t xml:space="preserve">㴌
 –
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
@@ -2844,8 +2841,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I8" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/밀양아리랑 (b1_110_1).xlsx
+++ b/sheets/대금율보/검수/밀양아리랑 (b1_110_1).xlsx
@@ -2532,20 +2532,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="60.61" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="90.2" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="90.2" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="90.2" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="90.2" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="90.2" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="90.2" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="90.2" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="90.2" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="90.2" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="90.2" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="90.2" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3104,6 +3104,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
 </worksheet>
 </file>